--- a/Mediciones/RNA/Cruz/RUN2_CRUZ_2NO.xlsx
+++ b/Mediciones/RNA/Cruz/RUN2_CRUZ_2NO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\Cruz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B5907F-B570-4D93-B416-6A2F86A74B45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1208858E-0792-4400-B2CB-ECD2D0E81CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -440,6 +440,9 @@
     <t>sensors_n_now</t>
   </si>
   <si>
+    <t>RNA</t>
+  </si>
+  <si>
     <t>{
   "timestamp": "2026-07-18T22:21:09",
   "bounds": {
@@ -450,7 +453,7 @@
   },
   "serial": {
     "port": "COM7",
-    "baud": "460800",
+    "baud": "115200",
     "eol": "LF",
     "send_enabled": true
   },
@@ -541,9 +544,6 @@
   "run_id": "R20260718_222109",
   "repetition": 1
 }</t>
-  </si>
-  <si>
-    <t>RNA</t>
   </si>
 </sst>
 </file>
@@ -899,7 +899,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D2">
         <v>1.5847155876811611E-2</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D3">
         <v>1.5847155876811611E-2</v>
@@ -1110,7 +1110,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D4">
         <v>1.7832225991531191E-2</v>
@@ -1163,7 +1163,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D5">
         <v>1.7832225991531191E-2</v>
@@ -1216,7 +1216,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D6">
         <v>1.7832225991531191E-2</v>
@@ -1269,7 +1269,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7">
         <v>1.7832225991531191E-2</v>
@@ -1322,7 +1322,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D8">
         <v>1.7832225991531191E-2</v>
@@ -1375,7 +1375,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D9">
         <v>1.7832225991531191E-2</v>
@@ -1428,7 +1428,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D10">
         <v>1.7832225991531191E-2</v>
@@ -1481,7 +1481,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D11">
         <v>1.7832225991531191E-2</v>
@@ -1534,7 +1534,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12">
         <v>1.7832225991531191E-2</v>
@@ -1587,7 +1587,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D13">
         <v>1.7832225991531191E-2</v>
@@ -1640,7 +1640,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14">
         <v>1.7832225991531191E-2</v>
@@ -1693,7 +1693,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15">
         <v>1.7832225991531191E-2</v>
@@ -1746,7 +1746,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D16">
         <v>1.7832225991531191E-2</v>
@@ -1799,7 +1799,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D17">
         <v>1.8244834662302801E-2</v>
@@ -1852,7 +1852,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D18">
         <v>1.8244834662302801E-2</v>
@@ -1905,7 +1905,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D19">
         <v>1.8244834662302801E-2</v>
@@ -1958,7 +1958,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D20">
         <v>2.0919630139065261E-2</v>
@@ -2011,7 +2011,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D21">
         <v>2.4383154547661389E-2</v>
@@ -2064,7 +2064,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D22">
         <v>2.9071017291073621E-2</v>
@@ -2117,7 +2117,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D23">
         <v>0.1105926971371525</v>
@@ -2170,7 +2170,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D24">
         <v>0.65785788906920628</v>
@@ -2223,7 +2223,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D25">
         <v>0.97066954793922244</v>
@@ -2276,7 +2276,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D26">
         <v>0.97066954793922244</v>
@@ -2329,7 +2329,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D27">
         <v>0.97066954793922244</v>
@@ -2382,7 +2382,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D28">
         <v>0.97066954793922244</v>
@@ -2435,7 +2435,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29">
         <v>0.97066954793922244</v>
@@ -2488,7 +2488,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30">
         <v>0.97066954793922244</v>
@@ -2541,7 +2541,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31">
         <v>0.97066954793922244</v>
@@ -2594,7 +2594,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D32">
         <v>0.97066954793922244</v>
@@ -2647,7 +2647,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D33">
         <v>0.97066954793922244</v>
@@ -2700,7 +2700,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D34">
         <v>0.97066954793922244</v>
@@ -2753,7 +2753,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D35">
         <v>0.97066954793922244</v>
@@ -2806,7 +2806,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D36">
         <v>0.97066954793922244</v>
@@ -2859,7 +2859,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D37">
         <v>0.97066954793922244</v>
@@ -2912,7 +2912,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D38">
         <v>0.97066954793922244</v>
@@ -2965,7 +2965,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D39">
         <v>0.97066954793922244</v>
@@ -3018,7 +3018,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D40">
         <v>0.97066954793922244</v>
@@ -3071,7 +3071,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D41">
         <v>0.97066954793922244</v>
@@ -3124,7 +3124,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D42">
         <v>0.97066954793922244</v>
@@ -3177,7 +3177,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43">
         <v>0.97066954793922244</v>
@@ -3230,7 +3230,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D44">
         <v>0.97066954793922244</v>
@@ -3283,7 +3283,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D45">
         <v>0.97066954793922244</v>
@@ -3336,7 +3336,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D46">
         <v>0.97066954793922244</v>
@@ -3389,7 +3389,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D47">
         <v>0.97066954793922244</v>
@@ -3442,7 +3442,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D48">
         <v>0.97066954793922244</v>
@@ -3495,7 +3495,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D49">
         <v>0.97066954793922244</v>
@@ -3548,7 +3548,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D50">
         <v>0.97066954793922244</v>
@@ -3601,7 +3601,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D51">
         <v>0.97066954793922244</v>
@@ -3654,7 +3654,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D52">
         <v>0.97066954793922244</v>
@@ -3707,7 +3707,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D53">
         <v>0.97066954793922244</v>
@@ -3760,7 +3760,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D54">
         <v>0.97066954793922244</v>
@@ -3813,7 +3813,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D55">
         <v>0.97066954793922244</v>
@@ -3866,7 +3866,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D56">
         <v>0.97066954793922244</v>
@@ -3919,7 +3919,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D57">
         <v>0.97066954793922244</v>
@@ -3972,7 +3972,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D58">
         <v>0.97066954793922244</v>
@@ -4025,7 +4025,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D59">
         <v>0.97066954793922244</v>
@@ -4078,7 +4078,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D60">
         <v>0.97066954793922244</v>
@@ -4131,7 +4131,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D61">
         <v>0.97066954793922244</v>
@@ -4184,7 +4184,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D62">
         <v>0.97066954793922244</v>
@@ -4237,7 +4237,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D63">
         <v>0.97066954793922244</v>
@@ -4290,7 +4290,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D64">
         <v>0.97066954793922244</v>
@@ -4343,7 +4343,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D65">
         <v>0.97066954793922244</v>
@@ -4396,7 +4396,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D66">
         <v>0.97066954793922244</v>
@@ -4449,7 +4449,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D67">
         <v>0.97066954793922244</v>
@@ -4502,7 +4502,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D68">
         <v>0.97066954793922244</v>
@@ -4555,7 +4555,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D69">
         <v>0.97066954793922244</v>
@@ -4608,7 +4608,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D70">
         <v>0.97066954793922244</v>
@@ -4661,7 +4661,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D71">
         <v>0.97066954793922244</v>
@@ -4714,7 +4714,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D72">
         <v>0.97066954793922244</v>
@@ -4767,7 +4767,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D73">
         <v>0.97066954793922244</v>
@@ -4820,7 +4820,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D74">
         <v>0.97066954793922244</v>
@@ -4873,7 +4873,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D75">
         <v>0.97066954793922244</v>
@@ -4926,7 +4926,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D76">
         <v>0.98873877516388597</v>
@@ -4979,7 +4979,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D77">
         <v>0.98873877516388597</v>
@@ -5032,7 +5032,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D78">
         <v>0.98873877516388597</v>
@@ -5085,7 +5085,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D79">
         <v>0.98873877516388597</v>
@@ -5138,7 +5138,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D80">
         <v>0.98873877516388597</v>
@@ -5191,7 +5191,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D81">
         <v>0.98873877516388597</v>
@@ -5244,7 +5244,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D82">
         <v>0.98873877516388597</v>
@@ -5297,7 +5297,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D83">
         <v>0.98873877516388597</v>
@@ -5350,7 +5350,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D84">
         <v>0.98873877516388597</v>
@@ -5403,7 +5403,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D85">
         <v>0.98873877516388597</v>
@@ -5456,7 +5456,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D86">
         <v>0.98873877516388597</v>
@@ -5509,7 +5509,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D87">
         <v>0.98873877516388597</v>
@@ -5562,7 +5562,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D88">
         <v>0.98873877516388597</v>
@@ -5615,7 +5615,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D89">
         <v>0.98873877516388597</v>
@@ -5668,7 +5668,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D90">
         <v>0.98873877516388597</v>
@@ -5721,7 +5721,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D91">
         <v>0.98873877516388597</v>
@@ -5774,7 +5774,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D92">
         <v>0.98873877516388597</v>
@@ -5827,7 +5827,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D93">
         <v>0.98873877516388597</v>
@@ -5880,7 +5880,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D94">
         <v>0.98873877516388597</v>
@@ -5933,7 +5933,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D95">
         <v>0.98873877516388597</v>
@@ -5986,7 +5986,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D96">
         <v>0.98873877516388597</v>
@@ -6039,7 +6039,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D97">
         <v>0.98873877516388597</v>
@@ -6092,7 +6092,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D98">
         <v>0.98873877516388597</v>
@@ -6145,7 +6145,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D99">
         <v>0.98873877516388597</v>
@@ -6198,7 +6198,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D100">
         <v>0.98873877516388597</v>
@@ -6251,7 +6251,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D101">
         <v>0.98873877516388597</v>
@@ -6304,7 +6304,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D102">
         <v>0.98873877516388597</v>
@@ -6357,7 +6357,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D103">
         <v>0.98873877516388597</v>
@@ -6410,7 +6410,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D104">
         <v>0.98873877516388597</v>
@@ -6463,7 +6463,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D105">
         <v>0.98873877516388597</v>
@@ -6516,7 +6516,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D106">
         <v>0.98873877516388597</v>
@@ -6569,7 +6569,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D107">
         <v>0.98873877516388597</v>
@@ -6622,7 +6622,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D108">
         <v>0.98873877516388597</v>
@@ -6675,7 +6675,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D109">
         <v>0.98873877516388597</v>
@@ -6728,7 +6728,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D110">
         <v>0.98873877516388597</v>
@@ -6781,7 +6781,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D111">
         <v>0.98873877516388597</v>
@@ -6834,7 +6834,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D112">
         <v>0.98873877516388597</v>
@@ -6887,7 +6887,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D113">
         <v>0.98873877516388597</v>
@@ -6940,7 +6940,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D114">
         <v>0.98873877516388597</v>
@@ -6993,7 +6993,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D115">
         <v>0.98873877516388597</v>
@@ -7046,7 +7046,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D116">
         <v>0.98873877516388597</v>
@@ -7099,7 +7099,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D117">
         <v>0.98873877516388597</v>
@@ -7152,7 +7152,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D118">
         <v>0.98873877516388597</v>
@@ -7205,7 +7205,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D119">
         <v>0.98873877516388597</v>
@@ -7258,7 +7258,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D120">
         <v>0.98873877516388597</v>
@@ -7311,7 +7311,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D121">
         <v>0.98873877516388597</v>
@@ -15172,7 +15172,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
